--- a/data/trans_camb/P1402-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P1402-Habitat-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4,38</t>
+          <t>4,34</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,79</t>
+          <t>3,68</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4,08</t>
+          <t>4,01</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 3,75</t>
+          <t>-1,59; 3,65</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,88; 6,74</t>
+          <t>1,06; 6,56</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,73; 6,98</t>
+          <t>1,58; 6,85</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 3,69</t>
+          <t>-1,33; 3,63</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 5,04</t>
+          <t>-0,55; 5,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,48; 5,99</t>
+          <t>1,26; 5,91</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 3,08</t>
+          <t>-0,8; 3,09</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,25; 5,01</t>
+          <t>0,94; 5,19</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,38; 5,79</t>
+          <t>2,09; 5,74</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>76,15%</t>
+          <t>75,58%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>62,86%</t>
+          <t>60,99%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>69,28%</t>
+          <t>68,03%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-21,89; 82,74</t>
+          <t>-24,12; 75,24</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12,23; 155,15</t>
+          <t>14,33; 141,49</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23,0; 152,76</t>
+          <t>22,38; 148,31</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-21,6; 73,98</t>
+          <t>-19,08; 75,58</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-9,31; 106,79</t>
+          <t>-9,85; 96,42</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,75; 125,85</t>
+          <t>14,67; 125,56</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-11,44; 61,56</t>
+          <t>-11,33; 60,87</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>18,24; 100,76</t>
+          <t>13,35; 101,83</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>35,1; 117,09</t>
+          <t>28,53; 112,7</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,23</t>
+          <t>2,09</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,1</t>
+          <t>0,07</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,11</t>
+          <t>1,07</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 2,01</t>
+          <t>-2,35; 2,15</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 4,01</t>
+          <t>-0,65; 4,03</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,87; 3,03</t>
+          <t>-0,31; 4,29</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 2,8</t>
+          <t>-2,07; 2,81</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 3,04</t>
+          <t>-2,4; 2,72</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 2,34</t>
+          <t>-2,15; 2,17</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 1,61</t>
+          <t>-1,71; 1,71</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 2,6</t>
+          <t>-0,82; 2,65</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,0; 1,84</t>
+          <t>-0,49; 2,72</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>30,98%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>14,65%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-32,36; 36,51</t>
+          <t>-30,53; 37,75</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-8,72; 71,25</t>
+          <t>-8,39; 74,08</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-49,45; 49,22</t>
+          <t>-3,92; 76,99</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-25,66; 41,55</t>
+          <t>-23,31; 42,98</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-22,53; 45,77</t>
+          <t>-25,59; 42,19</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-23,2; 35,98</t>
+          <t>-22,88; 33,82</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-22,37; 25,49</t>
+          <t>-21,01; 26,45</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-10,75; 40,89</t>
+          <t>-9,23; 41,38</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-36,93; 26,97</t>
+          <t>-6,09; 41,94</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4,6</t>
+          <t>4,46</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-1,66</t>
+          <t>-0,22</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1,18</t>
+          <t>2,11</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,34; 5,62</t>
+          <t>0,18; 5,57</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,61; 8,37</t>
+          <t>3,0; 8,2</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,12; 7,05</t>
+          <t>2,09; 6,95</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 4,23</t>
+          <t>-0,59; 4,6</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 5,04</t>
+          <t>-0,29; 5,19</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,25; 0,63</t>
+          <t>-2,48; 1,88</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,49; 4,25</t>
+          <t>0,75; 4,23</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,85; 5,83</t>
+          <t>1,9; 5,8</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 3,06</t>
+          <t>0,46; 3,76</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>104,62%</t>
+          <t>101,44%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-25,04%</t>
+          <t>-3,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>38,24%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,37; 156,27</t>
+          <t>1,83; 171,96</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>42,47; 257,3</t>
+          <t>51,6; 238,52</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>35,33; 209,47</t>
+          <t>34,87; 203,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-13,58; 74,22</t>
+          <t>-8,37; 87,46</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-7,87; 96,45</t>
+          <t>-3,84; 97,71</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-64,4; 10,13</t>
+          <t>-29,78; 36,06</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,89; 87,11</t>
+          <t>11,2; 90,39</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>26,81; 122,07</t>
+          <t>28,57; 121,71</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-23,84; 64,21</t>
+          <t>6,28; 81,52</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4,27</t>
+          <t>4,23</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,49</t>
+          <t>1,12</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2,24</t>
+          <t>2,59</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,4; 6,31</t>
+          <t>1,62; 6,23</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,22; 4,45</t>
+          <t>0,33; 4,45</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,92; 6,49</t>
+          <t>2,07; 6,3</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,55; 6,43</t>
+          <t>1,49; 6,58</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 4,54</t>
+          <t>-0,17; 4,37</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 2,48</t>
+          <t>-0,82; 3,12</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,2; 5,6</t>
+          <t>2,24; 5,72</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,76; 3,9</t>
+          <t>0,59; 3,78</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,8; 3,77</t>
+          <t>1,19; 4,09</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>79,32%</t>
+          <t>78,57%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>38,0%</t>
+          <t>43,95%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>23,08; 144,8</t>
+          <t>25,5; 135,81</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,04; 100,6</t>
+          <t>4,1; 96,31</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>28,21; 144,9</t>
+          <t>31,85; 144,12</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>20,15; 122,49</t>
+          <t>18,54; 123,54</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 85,35</t>
+          <t>-2,19; 84,33</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-23,04; 46,5</t>
+          <t>-11,38; 61,55</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>33,02; 110,88</t>
+          <t>33,21; 109,5</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>11,22; 74,3</t>
+          <t>8,58; 70,54</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>12,05; 71,35</t>
+          <t>17,63; 79,7</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3,03</t>
+          <t>3,65</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,43</t>
+          <t>1,04</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>1,7</t>
+          <t>2,31</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,49; 3,07</t>
+          <t>0,62; 3,06</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,97; 4,55</t>
+          <t>1,86; 4,31</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,27; 4,45</t>
+          <t>2,41; 4,83</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,64; 3,16</t>
+          <t>0,58; 3,12</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,89</t>
+          <t>0,29; 3,12</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 1,58</t>
+          <t>-0,05; 2,16</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,02; 2,79</t>
+          <t>0,95; 2,68</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,44; 3,23</t>
+          <t>1,44; 3,17</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,59; 2,69</t>
+          <t>1,46; 3,07</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>53,47%</t>
+          <t>64,47%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>37,13%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>8,88; 60,65</t>
+          <t>9,71; 58,84</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>30,48; 88,73</t>
+          <t>30,07; 84,61</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>20,49; 83,89</t>
+          <t>38,54; 92,21</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>8,86; 51,2</t>
+          <t>7,9; 50,77</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>3,73; 45,97</t>
+          <t>3,61; 50,65</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-17,19; 25,61</t>
+          <t>-0,5; 35,9</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>15,27; 47,76</t>
+          <t>14,23; 45,68</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>21,52; 55,8</t>
+          <t>21,24; 53,77</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>9,21; 46,0</t>
+          <t>22,0; 53,06</t>
         </is>
       </c>
     </row>
